--- a/tame_output/ON/bt/strategyON_20231207.xlsx
+++ b/tame_output/ON/bt/strategyON_20231207.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>407.7%</t>
+          <t>407.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.0%</t>
         </is>
       </c>
     </row>
@@ -41852,7 +41852,7 @@
         <v>45216</v>
       </c>
       <c r="B1754" t="n">
-        <v>2.864454936419491</v>
+        <v>2.864454936419492</v>
       </c>
       <c r="C1754" t="n">
         <v>2.957874679524909</v>
@@ -41875,7 +41875,7 @@
         <v>45217</v>
       </c>
       <c r="B1755" t="n">
-        <v>2.855532085778604</v>
+        <v>2.855532085778605</v>
       </c>
       <c r="C1755" t="n">
         <v>2.95420083304114</v>
@@ -41898,7 +41898,7 @@
         <v>45218</v>
       </c>
       <c r="B1756" t="n">
-        <v>2.890046240060275</v>
+        <v>2.890046240060276</v>
       </c>
       <c r="C1756" t="n">
         <v>2.969006534107256</v>
@@ -41944,7 +41944,7 @@
         <v>45220</v>
       </c>
       <c r="B1758" t="n">
-        <v>2.912903254947839</v>
+        <v>2.91290325494784</v>
       </c>
       <c r="C1758" t="n">
         <v>2.965146865274802</v>
@@ -41967,7 +41967,7 @@
         <v>45221</v>
       </c>
       <c r="B1759" t="n">
-        <v>2.94063219676755</v>
+        <v>2.940632196767551</v>
       </c>
       <c r="C1759" t="n">
         <v>2.964689051375926</v>
@@ -41990,7 +41990,7 @@
         <v>45222</v>
       </c>
       <c r="B1760" t="n">
-        <v>3.048806209055148</v>
+        <v>3.04880620905515</v>
       </c>
       <c r="C1760" t="n">
         <v>2.992474709334104</v>
@@ -42013,7 +42013,7 @@
         <v>45223</v>
       </c>
       <c r="B1761" t="n">
-        <v>3.046980105223824</v>
+        <v>3.046980105223825</v>
       </c>
       <c r="C1761" t="n">
         <v>3.010249418375564</v>
@@ -42036,7 +42036,7 @@
         <v>45224</v>
       </c>
       <c r="B1762" t="n">
-        <v>3.070330524157811</v>
+        <v>3.070330524157812</v>
       </c>
       <c r="C1762" t="n">
         <v>3.010722978056604</v>
@@ -42059,7 +42059,7 @@
         <v>45225</v>
       </c>
       <c r="B1763" t="n">
-        <v>3.050895742336374</v>
+        <v>3.050895742336375</v>
       </c>
       <c r="C1763" t="n">
         <v>3.016062350193502</v>
@@ -42082,7 +42082,7 @@
         <v>45226</v>
       </c>
       <c r="B1764" t="n">
-        <v>3.049222094320087</v>
+        <v>3.049222094320088</v>
       </c>
       <c r="C1764" t="n">
         <v>3.030639375029551</v>
@@ -42105,7 +42105,7 @@
         <v>45227</v>
       </c>
       <c r="B1765" t="n">
-        <v>3.046605534538361</v>
+        <v>3.046605534538362</v>
       </c>
       <c r="C1765" t="n">
         <v>3.030564355893199</v>
@@ -42128,7 +42128,7 @@
         <v>45228</v>
       </c>
       <c r="B1766" t="n">
-        <v>3.055423383477761</v>
+        <v>3.055423383477762</v>
       </c>
       <c r="C1766" t="n">
         <v>3.028879780391293</v>
@@ -42151,7 +42151,7 @@
         <v>45229</v>
       </c>
       <c r="B1767" t="n">
-        <v>3.053640504831978</v>
+        <v>3.053640504831979</v>
       </c>
       <c r="C1767" t="n">
         <v>3.033268356072139</v>
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.059751997255679</v>
+        <v>3.05975199725568</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227612</v>
+        <v>3.093259956227613</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42220,7 +42220,7 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.068246518571589</v>
+        <v>3.06824651857159</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708493</v>
+        <v>3.085392865708494</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066011</v>
+        <v>3.074518669066012</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.08750545129302</v>
+        <v>3.087505451293021</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239773</v>
+        <v>3.125945945239774</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42381,7 +42381,7 @@
         <v>45239</v>
       </c>
       <c r="B1777" t="n">
-        <v>3.128298755003008</v>
+        <v>3.128298755003009</v>
       </c>
       <c r="C1777" t="n">
         <v>3.084316661211631</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.13555534016786</v>
+        <v>3.135555340167861</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216941</v>
+        <v>3.134141625216942</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454037</v>
+        <v>3.132018996454038</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780866</v>
+        <v>3.120443325780867</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537929</v>
+        <v>3.09520660653793</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597765</v>
+        <v>3.147410092597766</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527684</v>
+        <v>3.120684616527685</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844643</v>
+        <v>3.118866618844644</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.123416866373819</v>
+        <v>3.12341686637382</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502546</v>
+        <v>3.141819250502547</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728029</v>
+        <v>3.14673011872803</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702053</v>
+        <v>3.120735995702054</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487809</v>
+        <v>3.14605337248781</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.15777720152482</v>
+        <v>3.157777201524821</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.1572943800687</v>
+        <v>3.157294380068701</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714841</v>
+        <v>3.147014107714842</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666731</v>
+        <v>3.162269743666732</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097096</v>
+        <v>3.163432091097097</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762257</v>
+        <v>3.169279212762258</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963477</v>
+        <v>3.185514355963478</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742722</v>
+        <v>3.238767863742723</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589522</v>
+        <v>3.260068416589523</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872955</v>
+        <v>3.306739876872956</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,16 +43002,16 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>2.958519610546943</v>
+        <v>2.958519610546944</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>1.060807140343015</v>
+        <v>1.061628960350381</v>
       </c>
       <c r="E1804" t="n">
-        <v>3.513567689937458</v>
+        <v>3.513896417940404</v>
       </c>
       <c r="F1804" t="n">
         <v>1.44931938054938</v>

--- a/tame_output/ON/bt/strategyON_20231207.xlsx
+++ b/tame_output/ON/bt/strategyON_20231207.xlsx
@@ -595,12 +595,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.1%</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,22 +901,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -934,17 +934,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-188.6%</t>
+          <t>-230.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -977,32 +977,32 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>407.6%</t>
+          <t>516.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-61.0%</t>
+          <t>-84.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-40.4%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1087,17 +1087,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-64.0%</t>
+          <t>-80.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1130,47 +1130,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>7.3%</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-85.8%</t>
+          <t>-101.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1298,17 +1298,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.4%</t>
+          <t>-157.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-64.3%</t>
+          <t>-79.5%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>105.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1413,15 +1413,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>104.0%</t>
+          <t>100.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-24.2%</t>
         </is>
       </c>
     </row>
@@ -41858,16 +41858,16 @@
         <v>2.957874679524909</v>
       </c>
       <c r="D1754" t="n">
-        <v>-0.2837564108388138</v>
+        <v>-0.7051098269997308</v>
       </c>
       <c r="E1754" t="n">
-        <v>2.844015690875636</v>
+        <v>2.675474324411269</v>
       </c>
       <c r="F1754" t="n">
-        <v>1.317514017604929</v>
+        <v>1.165826794388025</v>
       </c>
       <c r="G1754" t="n">
-        <v>3.748383090087867</v>
+        <v>3.657370756157725</v>
       </c>
     </row>
     <row r="1755">
@@ -41881,16 +41881,16 @@
         <v>2.95420083304114</v>
       </c>
       <c r="D1755" t="n">
-        <v>-0.2757712424570693</v>
+        <v>-0.6971246586179863</v>
       </c>
       <c r="E1755" t="n">
-        <v>2.843535911744566</v>
+        <v>2.674994545280199</v>
       </c>
       <c r="F1755" t="n">
-        <v>1.319741563641705</v>
+        <v>1.168054340424802</v>
       </c>
       <c r="G1755" t="n">
-        <v>3.746045771226165</v>
+        <v>3.655033437296023</v>
       </c>
     </row>
     <row r="1756">
@@ -41904,16 +41904,16 @@
         <v>2.969006534107256</v>
       </c>
       <c r="D1756" t="n">
-        <v>-0.286657606228113</v>
+        <v>-0.70801102238903</v>
       </c>
       <c r="E1756" t="n">
-        <v>2.853987067302264</v>
+        <v>2.685445700837897</v>
       </c>
       <c r="F1756" t="n">
-        <v>1.319741563641705</v>
+        <v>1.168054340424802</v>
       </c>
       <c r="G1756" t="n">
-        <v>3.760851472292281</v>
+        <v>3.669839138362139</v>
       </c>
     </row>
     <row r="1757">
@@ -41927,16 +41927,16 @@
         <v>2.968547780644436</v>
       </c>
       <c r="D1757" t="n">
-        <v>-0.2785404662704678</v>
+        <v>-0.6998938824313848</v>
       </c>
       <c r="E1757" t="n">
-        <v>2.856775169822502</v>
+        <v>2.688233803358135</v>
       </c>
       <c r="F1757" t="n">
-        <v>1.319741563641705</v>
+        <v>1.168054340424802</v>
       </c>
       <c r="G1757" t="n">
-        <v>3.760392718829461</v>
+        <v>3.669380384899319</v>
       </c>
     </row>
     <row r="1758">
@@ -41950,16 +41950,16 @@
         <v>2.965146865274802</v>
       </c>
       <c r="D1758" t="n">
-        <v>-0.2740311180446826</v>
+        <v>-0.6953845342055996</v>
       </c>
       <c r="E1758" t="n">
-        <v>2.855177993743182</v>
+        <v>2.686636627278816</v>
       </c>
       <c r="F1758" t="n">
-        <v>1.319741563641705</v>
+        <v>1.168054340424802</v>
       </c>
       <c r="G1758" t="n">
-        <v>3.756991803459827</v>
+        <v>3.665979469529685</v>
       </c>
     </row>
     <row r="1759">
@@ -41973,16 +41973,16 @@
         <v>2.964689051375926</v>
       </c>
       <c r="D1759" t="n">
-        <v>-0.2843382437021177</v>
+        <v>-0.7056916598630347</v>
       </c>
       <c r="E1759" t="n">
-        <v>2.850597329581332</v>
+        <v>2.682055963116965</v>
       </c>
       <c r="F1759" t="n">
-        <v>1.312743181326852</v>
+        <v>1.161055958109948</v>
       </c>
       <c r="G1759" t="n">
-        <v>3.752334960172039</v>
+        <v>3.661322626241897</v>
       </c>
     </row>
     <row r="1760">
@@ -41996,16 +41996,16 @@
         <v>2.992474709334104</v>
       </c>
       <c r="D1760" t="n">
-        <v>-0.3325808925878297</v>
+        <v>-0.7539343087487467</v>
       </c>
       <c r="E1760" t="n">
-        <v>2.859085927985225</v>
+        <v>2.690544561520858</v>
       </c>
       <c r="F1760" t="n">
-        <v>1.312743181326852</v>
+        <v>1.161055958109948</v>
       </c>
       <c r="G1760" t="n">
-        <v>3.780120618130216</v>
+        <v>3.689108284200075</v>
       </c>
     </row>
     <row r="1761">
@@ -42019,16 +42019,16 @@
         <v>3.010249418375564</v>
       </c>
       <c r="D1761" t="n">
-        <v>-0.3254828916203281</v>
+        <v>-0.746836307781245</v>
       </c>
       <c r="E1761" t="n">
-        <v>2.879699837413686</v>
+        <v>2.711158470949319</v>
       </c>
       <c r="F1761" t="n">
-        <v>1.312850379438228</v>
+        <v>1.161163156221324</v>
       </c>
       <c r="G1761" t="n">
-        <v>3.797959646038502</v>
+        <v>3.70694731210836</v>
       </c>
     </row>
     <row r="1762">
@@ -42042,16 +42042,16 @@
         <v>3.010722978056604</v>
       </c>
       <c r="D1762" t="n">
-        <v>-0.3242798253242217</v>
+        <v>-0.7456332414851385</v>
       </c>
       <c r="E1762" t="n">
-        <v>2.880654623613169</v>
+        <v>2.712113257148802</v>
       </c>
       <c r="F1762" t="n">
-        <v>1.312850379438228</v>
+        <v>1.161163156221324</v>
       </c>
       <c r="G1762" t="n">
-        <v>3.798433205719543</v>
+        <v>3.707420871789401</v>
       </c>
     </row>
     <row r="1763">
@@ -42065,16 +42065,16 @@
         <v>3.016062350193502</v>
       </c>
       <c r="D1763" t="n">
-        <v>-0.3219267779909762</v>
+        <v>-0.7432801941518931</v>
       </c>
       <c r="E1763" t="n">
-        <v>2.886935214683364</v>
+        <v>2.718393848218998</v>
       </c>
       <c r="F1763" t="n">
-        <v>1.315203426771473</v>
+        <v>1.16351620355457</v>
       </c>
       <c r="G1763" t="n">
-        <v>3.805184406256387</v>
+        <v>3.714172072326245</v>
       </c>
     </row>
     <row r="1764">
@@ -42088,16 +42088,16 @@
         <v>3.030639375029551</v>
       </c>
       <c r="D1764" t="n">
-        <v>-0.32081049599975</v>
+        <v>-0.7421639121606669</v>
       </c>
       <c r="E1764" t="n">
-        <v>2.901958752315904</v>
+        <v>2.733417385851538</v>
       </c>
       <c r="F1764" t="n">
-        <v>1.316319708762699</v>
+        <v>1.164632485545796</v>
       </c>
       <c r="G1764" t="n">
-        <v>3.820431200287172</v>
+        <v>3.72941886635703</v>
       </c>
     </row>
     <row r="1765">
@@ -42111,16 +42111,16 @@
         <v>3.030564355893199</v>
       </c>
       <c r="D1765" t="n">
-        <v>-0.3170725399386946</v>
+        <v>-0.7384259560996115</v>
       </c>
       <c r="E1765" t="n">
-        <v>2.903378915603974</v>
+        <v>2.734837549139607</v>
       </c>
       <c r="F1765" t="n">
-        <v>1.318696161043324</v>
+        <v>1.167008937826421</v>
       </c>
       <c r="G1765" t="n">
-        <v>3.821782052519195</v>
+        <v>3.730769718589053</v>
       </c>
     </row>
     <row r="1766">
@@ -42134,16 +42134,16 @@
         <v>3.028879780391293</v>
       </c>
       <c r="D1766" t="n">
-        <v>-0.3085753942775614</v>
+        <v>-0.7299288104384782</v>
       </c>
       <c r="E1766" t="n">
-        <v>2.905093198366521</v>
+        <v>2.736551831902155</v>
       </c>
       <c r="F1766" t="n">
-        <v>1.318696161043324</v>
+        <v>1.167008937826421</v>
       </c>
       <c r="G1766" t="n">
-        <v>3.820097477017289</v>
+        <v>3.729085143087147</v>
       </c>
     </row>
     <row r="1767">
@@ -42157,16 +42157,16 @@
         <v>3.033268356072139</v>
       </c>
       <c r="D1767" t="n">
-        <v>-0.3082674341928368</v>
+        <v>-0.7296208503537536</v>
       </c>
       <c r="E1767" t="n">
-        <v>2.909604958081257</v>
+        <v>2.741063591616891</v>
       </c>
       <c r="F1767" t="n">
-        <v>1.319877875136024</v>
+        <v>1.168190651919121</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.825195081153755</v>
+        <v>3.734182747223613</v>
       </c>
     </row>
     <row r="1768">
@@ -42180,16 +42180,16 @@
         <v>3.034928653249013</v>
       </c>
       <c r="D1768" t="n">
-        <v>-0.3064856718222454</v>
+        <v>-0.7278390879831622</v>
       </c>
       <c r="E1768" t="n">
-        <v>2.911977960206368</v>
+        <v>2.743436593742002</v>
       </c>
       <c r="F1768" t="n">
-        <v>1.319877875136024</v>
+        <v>1.168190651919121</v>
       </c>
       <c r="G1768" t="n">
-        <v>3.82685537833063</v>
+        <v>3.735843044400487</v>
       </c>
     </row>
     <row r="1769">
@@ -42203,16 +42203,16 @@
         <v>3.049962823512704</v>
       </c>
       <c r="D1769" t="n">
-        <v>-0.3105630269593367</v>
+        <v>-0.7319164431202536</v>
       </c>
       <c r="E1769" t="n">
-        <v>2.925381188415222</v>
+        <v>2.756839821950855</v>
       </c>
       <c r="F1769" t="n">
-        <v>1.319877875136024</v>
+        <v>1.168190651919121</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.84188954859432</v>
+        <v>3.750877214664178</v>
       </c>
     </row>
     <row r="1770">
@@ -42226,16 +42226,16 @@
         <v>3.048277258176837</v>
       </c>
       <c r="D1770" t="n">
-        <v>-0.3005709460329276</v>
+        <v>-0.7219243621938445</v>
       </c>
       <c r="E1770" t="n">
-        <v>2.927692455449919</v>
+        <v>2.759151088985552</v>
       </c>
       <c r="F1770" t="n">
-        <v>1.329869956062433</v>
+        <v>1.17818273284553</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.846199231814298</v>
+        <v>3.755186897884156</v>
       </c>
     </row>
     <row r="1771">
@@ -42249,16 +42249,16 @@
         <v>3.051179068073428</v>
       </c>
       <c r="D1771" t="n">
-        <v>-0.3011267010889654</v>
+        <v>-0.7224801172498823</v>
       </c>
       <c r="E1771" t="n">
-        <v>2.930371963324095</v>
+        <v>2.761830596859729</v>
       </c>
       <c r="F1771" t="n">
-        <v>1.328262542301355</v>
+        <v>1.176575319084452</v>
       </c>
       <c r="G1771" t="n">
-        <v>3.848136593454243</v>
+        <v>3.757124259524101</v>
       </c>
     </row>
     <row r="1772">
@@ -42272,16 +42272,16 @@
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>-0.3043410535022769</v>
+        <v>-0.7256944696631937</v>
       </c>
       <c r="E1772" t="n">
-        <v>2.934611211497917</v>
+        <v>2.766069845033551</v>
       </c>
       <c r="F1772" t="n">
-        <v>1.328262542301355</v>
+        <v>1.176575319084452</v>
       </c>
       <c r="G1772" t="n">
-        <v>3.85366158259339</v>
+        <v>3.762649248663248</v>
       </c>
     </row>
     <row r="1773">
@@ -42295,16 +42295,16 @@
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>-0.3213492989048863</v>
+        <v>-0.7427027150658032</v>
       </c>
       <c r="E1773" t="n">
-        <v>2.928885485974605</v>
+        <v>2.760344119510239</v>
       </c>
       <c r="F1773" t="n">
-        <v>1.331261677314329</v>
+        <v>1.179574454097426</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.856538636238906</v>
+        <v>3.765526302308763</v>
       </c>
     </row>
     <row r="1774">
@@ -42318,16 +42318,16 @@
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>-0.3023895764535318</v>
+        <v>-0.7237429926144486</v>
       </c>
       <c r="E1774" t="n">
-        <v>2.93721923712642</v>
+        <v>2.768677870662053</v>
       </c>
       <c r="F1774" t="n">
-        <v>1.331261677314329</v>
+        <v>1.179574454097426</v>
       </c>
       <c r="G1774" t="n">
-        <v>3.857288498410179</v>
+        <v>3.766276164480036</v>
       </c>
     </row>
     <row r="1775">
@@ -42341,16 +42341,16 @@
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>-0.301154851850723</v>
+        <v>-0.7225082680116399</v>
       </c>
       <c r="E1775" t="n">
-        <v>2.935948724431124</v>
+        <v>2.767407357966758</v>
       </c>
       <c r="F1775" t="n">
-        <v>1.331261677314329</v>
+        <v>1.179574454097426</v>
       </c>
       <c r="G1775" t="n">
-        <v>3.85552409587376</v>
+        <v>3.764511761943617</v>
       </c>
     </row>
     <row r="1776">
@@ -42364,16 +42364,16 @@
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>-0.3111891156743717</v>
+        <v>-0.7325425318352886</v>
       </c>
       <c r="E1776" t="n">
-        <v>2.935502628738527</v>
+        <v>2.76696126227416</v>
       </c>
       <c r="F1776" t="n">
-        <v>1.331261677314329</v>
+        <v>1.179574454097426</v>
       </c>
       <c r="G1776" t="n">
-        <v>3.859091705710621</v>
+        <v>3.768079371780479</v>
       </c>
     </row>
     <row r="1777">
@@ -42387,16 +42387,16 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>-0.3162281139722384</v>
+        <v>-0.7375815301331554</v>
       </c>
       <c r="E1777" t="n">
-        <v>2.957468991308989</v>
+        <v>2.788927624844622</v>
       </c>
       <c r="F1777" t="n">
-        <v>1.326222679016462</v>
+        <v>1.174535455799559</v>
       </c>
       <c r="G1777" t="n">
-        <v>3.88005026862151</v>
+        <v>3.789037934691368</v>
       </c>
     </row>
     <row r="1778">
@@ -42410,16 +42410,16 @@
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>-0.3064083958116877</v>
+        <v>-0.7277618119726047</v>
       </c>
       <c r="E1778" t="n">
-        <v>2.958865590060439</v>
+        <v>2.790324223596072</v>
       </c>
       <c r="F1778" t="n">
-        <v>1.33265261923315</v>
+        <v>1.180965396016246</v>
       </c>
       <c r="G1778" t="n">
-        <v>3.881376944238752</v>
+        <v>3.79036461030861</v>
       </c>
     </row>
     <row r="1779">
@@ -42433,16 +42433,16 @@
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>-0.3046067689727338</v>
+        <v>-0.7259601851336508</v>
       </c>
       <c r="E1779" t="n">
-        <v>2.944834802799646</v>
+        <v>2.776293436335279</v>
       </c>
       <c r="F1779" t="n">
-        <v>1.33265261923315</v>
+        <v>1.180965396016246</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.866625506242378</v>
+        <v>3.775613172312236</v>
       </c>
     </row>
     <row r="1780">
@@ -42456,16 +42456,16 @@
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>-0.303618087228566</v>
+        <v>-0.724971503389483</v>
       </c>
       <c r="E1780" t="n">
-        <v>2.943344031812985</v>
+        <v>2.774802665348619</v>
       </c>
       <c r="F1780" t="n">
-        <v>1.33265261923315</v>
+        <v>1.180965396016246</v>
       </c>
       <c r="G1780" t="n">
-        <v>3.86473926255805</v>
+        <v>3.773726928627908</v>
       </c>
     </row>
     <row r="1781">
@@ -42479,16 +42479,16 @@
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-0.2956217327070274</v>
+        <v>-0.7169751488679444</v>
       </c>
       <c r="E1781" t="n">
-        <v>2.948516200077441</v>
+        <v>2.779974833613074</v>
       </c>
       <c r="F1781" t="n">
-        <v>1.340648973754688</v>
+        <v>1.188961750537785</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.871510701726813</v>
+        <v>3.780498367796671</v>
       </c>
     </row>
     <row r="1782">
@@ -42502,16 +42502,16 @@
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-0.2906379820351187</v>
+        <v>-0.7119913981960357</v>
       </c>
       <c r="E1782" t="n">
-        <v>2.962348280937116</v>
+        <v>2.79380691447275</v>
       </c>
       <c r="F1782" t="n">
-        <v>1.345632724426597</v>
+        <v>1.193945501209694</v>
       </c>
       <c r="G1782" t="n">
-        <v>3.886339532720871</v>
+        <v>3.795327198790728</v>
       </c>
     </row>
     <row r="1783">
@@ -42525,16 +42525,16 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-0.2842518430855632</v>
+        <v>-0.7056052592464802</v>
       </c>
       <c r="E1783" t="n">
-        <v>2.971630939528727</v>
+        <v>2.803089573064361</v>
       </c>
       <c r="F1783" t="n">
-        <v>1.345632724426597</v>
+        <v>1.193945501209694</v>
       </c>
       <c r="G1783" t="n">
-        <v>3.89306773573266</v>
+        <v>3.802055401802518</v>
       </c>
     </row>
     <row r="1784">
@@ -42548,16 +42548,16 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-0.2960571934041958</v>
+        <v>-0.7174106095651128</v>
       </c>
       <c r="E1784" t="n">
-        <v>2.970924888160817</v>
+        <v>2.80238352169645</v>
       </c>
       <c r="F1784" t="n">
-        <v>1.333827374107964</v>
+        <v>1.182140150891061</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.890000614301022</v>
+        <v>3.79898828037088</v>
       </c>
     </row>
     <row r="1785">
@@ -42571,16 +42571,16 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-0.2873253826255295</v>
+        <v>-0.7086787987864466</v>
       </c>
       <c r="E1785" t="n">
-        <v>2.980365070082173</v>
+        <v>2.811823703617806</v>
       </c>
       <c r="F1785" t="n">
-        <v>1.342559184886631</v>
+        <v>1.190871961669727</v>
       </c>
       <c r="G1785" t="n">
-        <v>3.901187158378112</v>
+        <v>3.810174824447969</v>
       </c>
     </row>
     <row r="1786">
@@ -42594,16 +42594,16 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-0.2809884959810776</v>
+        <v>-0.7023419121419946</v>
       </c>
       <c r="E1786" t="n">
-        <v>2.978210643687939</v>
+        <v>2.809669277223572</v>
       </c>
       <c r="F1786" t="n">
-        <v>1.342559184886631</v>
+        <v>1.190871961669727</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.896497977326097</v>
+        <v>3.805485643395955</v>
       </c>
     </row>
     <row r="1787">
@@ -42617,16 +42617,16 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-0.2784540482537092</v>
+        <v>-0.6998074644146263</v>
       </c>
       <c r="E1787" t="n">
-        <v>2.98918708058108</v>
+        <v>2.820645714116714</v>
       </c>
       <c r="F1787" t="n">
-        <v>1.342559184886631</v>
+        <v>1.190871961669727</v>
       </c>
       <c r="G1787" t="n">
-        <v>3.906460635128291</v>
+        <v>3.815448301198149</v>
       </c>
     </row>
     <row r="1788">
@@ -42640,16 +42640,16 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-0.2785299472343138</v>
+        <v>-0.6998833633952308</v>
       </c>
       <c r="E1788" t="n">
-        <v>2.981571401181748</v>
+        <v>2.813030034717381</v>
       </c>
       <c r="F1788" t="n">
-        <v>1.343322445575958</v>
+        <v>1.191635222359054</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.899333271734797</v>
+        <v>3.808320937804655</v>
       </c>
     </row>
     <row r="1789">
@@ -42663,16 +42663,16 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-0.2890321367936604</v>
+        <v>-0.7103855529545775</v>
       </c>
       <c r="E1789" t="n">
-        <v>2.955135101148383</v>
+        <v>2.786593734684016</v>
       </c>
       <c r="F1789" t="n">
-        <v>1.332820256016611</v>
+        <v>1.181133032799707</v>
       </c>
       <c r="G1789" t="n">
-        <v>3.870796533789562</v>
+        <v>3.77978419985942</v>
       </c>
     </row>
     <row r="1790">
@@ -42686,16 +42686,16 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-0.2908653994727767</v>
+        <v>-0.7122188156336938</v>
       </c>
       <c r="E1790" t="n">
-        <v>2.955102635922858</v>
+        <v>2.786561269458491</v>
       </c>
       <c r="F1790" t="n">
-        <v>1.332820256016611</v>
+        <v>1.181133032799707</v>
       </c>
       <c r="G1790" t="n">
-        <v>3.871497373635683</v>
+        <v>3.780485039705542</v>
       </c>
     </row>
     <row r="1791">
@@ -42709,16 +42709,16 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-0.2958745145343607</v>
+        <v>-0.7172279306952778</v>
       </c>
       <c r="E1791" t="n">
-        <v>2.953616069727083</v>
+        <v>2.785074703262717</v>
       </c>
       <c r="F1791" t="n">
-        <v>1.331825678458076</v>
+        <v>1.180138455241173</v>
       </c>
       <c r="G1791" t="n">
-        <v>3.871417706929422</v>
+        <v>3.78040537299928</v>
       </c>
     </row>
     <row r="1792">
@@ -42732,16 +42732,16 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-0.2995800711711753</v>
+        <v>-0.7209334873320924</v>
       </c>
       <c r="E1792" t="n">
-        <v>2.951361572312723</v>
+        <v>2.782820205848356</v>
       </c>
       <c r="F1792" t="n">
-        <v>1.329956003200441</v>
+        <v>1.178268779983538</v>
       </c>
       <c r="G1792" t="n">
-        <v>3.869523627015206</v>
+        <v>3.778511293085065</v>
       </c>
     </row>
     <row r="1793">
@@ -42755,16 +42755,16 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-0.2983477458138098</v>
+        <v>-0.7197011619747269</v>
       </c>
       <c r="E1793" t="n">
-        <v>2.952274354517989</v>
+        <v>2.783732988053622</v>
       </c>
       <c r="F1793" t="n">
-        <v>1.330586379572479</v>
+        <v>1.178899156355576</v>
       </c>
       <c r="G1793" t="n">
-        <v>3.870321704900749</v>
+        <v>3.779309370970606</v>
       </c>
     </row>
     <row r="1794">
@@ -42778,16 +42778,16 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-0.2880197487979576</v>
+        <v>-0.7093731649588747</v>
       </c>
       <c r="E1794" t="n">
-        <v>2.960535461488543</v>
+        <v>2.791994095024176</v>
       </c>
       <c r="F1794" t="n">
-        <v>1.340914376588331</v>
+        <v>1.189227153371428</v>
       </c>
       <c r="G1794" t="n">
-        <v>3.880648411274473</v>
+        <v>3.789636077344331</v>
       </c>
     </row>
     <row r="1795">
@@ -42801,16 +42801,16 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-0.2879034136504019</v>
+        <v>-0.709256829811319</v>
       </c>
       <c r="E1795" t="n">
-        <v>2.967102655749402</v>
+        <v>2.798561289285035</v>
       </c>
       <c r="F1795" t="n">
-        <v>1.341030711735887</v>
+        <v>1.189343488518984</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.887238872564843</v>
+        <v>3.796226538634701</v>
       </c>
     </row>
     <row r="1796">
@@ -42824,16 +42824,16 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-0.2897488232272695</v>
+        <v>-0.7111022393881865</v>
       </c>
       <c r="E1796" t="n">
-        <v>2.963338462364043</v>
+        <v>2.794797095899677</v>
       </c>
       <c r="F1796" t="n">
-        <v>1.341030711735887</v>
+        <v>1.189343488518984</v>
       </c>
       <c r="G1796" t="n">
-        <v>3.884212843010232</v>
+        <v>3.79320050908009</v>
       </c>
     </row>
     <row r="1797">
@@ -42847,16 +42847,16 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-0.2882503907021706</v>
+        <v>-0.7096038068630877</v>
       </c>
       <c r="E1797" t="n">
-        <v>2.963876123235216</v>
+        <v>2.79533475677085</v>
       </c>
       <c r="F1797" t="n">
-        <v>1.342529144260986</v>
+        <v>1.190841921044082</v>
       </c>
       <c r="G1797" t="n">
-        <v>3.885050190386425</v>
+        <v>3.794037856456282</v>
       </c>
     </row>
     <row r="1798">
@@ -42870,16 +42870,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-0.2963146428949044</v>
+        <v>-0.7176680590558215</v>
       </c>
       <c r="E1798" t="n">
-        <v>2.961928400301434</v>
+        <v>2.793387033837067</v>
       </c>
       <c r="F1798" t="n">
-        <v>1.334464892068252</v>
+        <v>1.182777668851348</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.881489617014096</v>
+        <v>3.790477283083954</v>
       </c>
     </row>
     <row r="1799">
@@ -42893,16 +42893,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-0.2976446103561167</v>
+        <v>-0.7189980265170339</v>
       </c>
       <c r="E1799" t="n">
-        <v>2.961396413316949</v>
+        <v>2.792855046852583</v>
       </c>
       <c r="F1799" t="n">
-        <v>1.334464892068252</v>
+        <v>1.182777668851348</v>
       </c>
       <c r="G1799" t="n">
-        <v>3.881489617014096</v>
+        <v>3.790477283083954</v>
       </c>
     </row>
     <row r="1800">
@@ -42916,16 +42916,16 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-0.0697799276226056</v>
+        <v>-0.4911333437835228</v>
       </c>
       <c r="E1800" t="n">
-        <v>3.054758759517516</v>
+        <v>2.886217393053149</v>
       </c>
       <c r="F1800" t="n">
-        <v>1.334464892068252</v>
+        <v>1.182777668851348</v>
       </c>
       <c r="G1800" t="n">
-        <v>3.883706090121258</v>
+        <v>3.792693756191116</v>
       </c>
     </row>
     <row r="1801">
@@ -42939,16 +42939,16 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>0.1783216362446112</v>
+        <v>-0.243031779916306</v>
       </c>
       <c r="E1801" t="n">
-        <v>3.161533981409495</v>
+        <v>2.992992614945128</v>
       </c>
       <c r="F1801" t="n">
-        <v>1.334464892068252</v>
+        <v>1.182777668851348</v>
       </c>
       <c r="G1801" t="n">
-        <v>3.89124068646635</v>
+        <v>3.800228352536208</v>
       </c>
     </row>
     <row r="1802">
@@ -42962,16 +42962,16 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>0.4751600356379416</v>
+        <v>0.05380661947702436</v>
       </c>
       <c r="E1802" t="n">
-        <v>3.281692352140285</v>
+        <v>3.113150985675918</v>
       </c>
       <c r="F1802" t="n">
-        <v>1.44931938054938</v>
+        <v>1.297632157332476</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.961576390528484</v>
+        <v>3.870564056598342</v>
       </c>
     </row>
     <row r="1803">
@@ -42985,16 +42985,16 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>0.7787995924633782</v>
+        <v>0.3574461763024609</v>
       </c>
       <c r="E1803" t="n">
-        <v>3.404825249336146</v>
+        <v>3.236283882871779</v>
       </c>
       <c r="F1803" t="n">
-        <v>1.44931938054938</v>
+        <v>1.297632157332476</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.96325346499417</v>
+        <v>3.872241131064028</v>
       </c>
     </row>
     <row r="1804">
@@ -43002,22 +43002,22 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>2.958519610546944</v>
+        <v>2.956121583305116</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>1.061628960350381</v>
+        <v>1.019887870588557</v>
       </c>
       <c r="E1804" t="n">
-        <v>3.513896417940404</v>
+        <v>3.497199982035675</v>
       </c>
       <c r="F1804" t="n">
-        <v>1.44931938054938</v>
+        <v>1.297632157332476</v>
       </c>
       <c r="G1804" t="n">
-        <v>3.959192886443629</v>
+        <v>3.868180552513486</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231207.xlsx
+++ b/tame_output/ON/bt/strategyON_20231207.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>516.4%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-40.4%</t>
+          <t>-77.8%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1140,32 +1140,32 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>-7.6%</t>
         </is>
       </c>
     </row>
@@ -41852,7 +41852,7 @@
         <v>45216</v>
       </c>
       <c r="B1754" t="n">
-        <v>2.864454936419492</v>
+        <v>2.864454936419491</v>
       </c>
       <c r="C1754" t="n">
         <v>2.957874679524909</v>
@@ -41990,7 +41990,7 @@
         <v>45222</v>
       </c>
       <c r="B1760" t="n">
-        <v>3.04880620905515</v>
+        <v>3.048806209055149</v>
       </c>
       <c r="C1760" t="n">
         <v>2.992474709334104</v>
@@ -42013,7 +42013,7 @@
         <v>45223</v>
       </c>
       <c r="B1761" t="n">
-        <v>3.046980105223825</v>
+        <v>3.046980105223824</v>
       </c>
       <c r="C1761" t="n">
         <v>3.010249418375564</v>
@@ -42036,7 +42036,7 @@
         <v>45224</v>
       </c>
       <c r="B1762" t="n">
-        <v>3.070330524157812</v>
+        <v>3.070330524157811</v>
       </c>
       <c r="C1762" t="n">
         <v>3.010722978056604</v>
@@ -42059,7 +42059,7 @@
         <v>45225</v>
       </c>
       <c r="B1763" t="n">
-        <v>3.050895742336375</v>
+        <v>3.050895742336374</v>
       </c>
       <c r="C1763" t="n">
         <v>3.016062350193502</v>
@@ -42082,7 +42082,7 @@
         <v>45226</v>
       </c>
       <c r="B1764" t="n">
-        <v>3.049222094320088</v>
+        <v>3.049222094320087</v>
       </c>
       <c r="C1764" t="n">
         <v>3.030639375029551</v>
@@ -42105,7 +42105,7 @@
         <v>45227</v>
       </c>
       <c r="B1765" t="n">
-        <v>3.046605534538362</v>
+        <v>3.046605534538361</v>
       </c>
       <c r="C1765" t="n">
         <v>3.030564355893199</v>
@@ -42128,7 +42128,7 @@
         <v>45228</v>
       </c>
       <c r="B1766" t="n">
-        <v>3.055423383477762</v>
+        <v>3.055423383477761</v>
       </c>
       <c r="C1766" t="n">
         <v>3.028879780391293</v>
@@ -42151,7 +42151,7 @@
         <v>45229</v>
       </c>
       <c r="B1767" t="n">
-        <v>3.053640504831979</v>
+        <v>3.053640504831978</v>
       </c>
       <c r="C1767" t="n">
         <v>3.033268356072139</v>
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.05975199725568</v>
+        <v>3.059751997255679</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227613</v>
+        <v>3.093259956227612</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42220,7 +42220,7 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.06824651857159</v>
+        <v>3.068246518571589</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708494</v>
+        <v>3.085392865708493</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066012</v>
+        <v>3.074518669066011</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293021</v>
+        <v>3.08750545129302</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239774</v>
+        <v>3.125945945239773</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42381,7 +42381,7 @@
         <v>45239</v>
       </c>
       <c r="B1777" t="n">
-        <v>3.128298755003009</v>
+        <v>3.128298755003008</v>
       </c>
       <c r="C1777" t="n">
         <v>3.084316661211631</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167861</v>
+        <v>3.13555534016786</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216942</v>
+        <v>3.134141625216941</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454038</v>
+        <v>3.132018996454037</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780867</v>
+        <v>3.120443325780866</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.09520660653793</v>
+        <v>3.095206606537929</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597766</v>
+        <v>3.147410092597765</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527685</v>
+        <v>3.120684616527684</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844644</v>
+        <v>3.118866618844643</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.12341686637382</v>
+        <v>3.123416866373819</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502547</v>
+        <v>3.141819250502546</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.14673011872803</v>
+        <v>3.146730118728029</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702054</v>
+        <v>3.120735995702053</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.14605337248781</v>
+        <v>3.146053372487808</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524821</v>
+        <v>3.15777720152482</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068701</v>
+        <v>3.1572943800687</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963478</v>
+        <v>3.185514355963479</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -43008,10 +43008,10 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>1.019887870588557</v>
+        <v>0.6464667827431695</v>
       </c>
       <c r="E1804" t="n">
-        <v>3.497199982035675</v>
+        <v>3.347831546897519</v>
       </c>
       <c r="F1804" t="n">
         <v>1.297632157332476</v>
